--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104723_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104723_W30.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7093</v>
+        <v>4.2561</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1692</v>
+        <v>2.3309</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5401</v>
+        <v>1.9252</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8739</v>
+        <v>2.8728</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0677</v>
+        <v>2.0652</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8062</v>
+        <v>0.8076</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5631</v>
+        <v>2.5566</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4885</v>
+        <v>2.4821</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3109</v>
+        <v>0.3162</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4208</v>
+        <v>-0.4169</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1307</v>
+        <v>1.6792</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1964</v>
+        <v>1.3677</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.3115</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0992</v>
+        <v>1.572</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0179</v>
+        <v>0.7905</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1171</v>
+        <v>0.7814</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.8168</v>
+        <v>-0.0466</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3329</v>
+        <v>1.037</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.4839</v>
+        <v>-1.0836</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.6861</v>
+        <v>1.4001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4312</v>
+        <v>1.8853</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.2549</v>
+        <v>-0.4852</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1307</v>
+        <v>-1.4467</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.229</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5903</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9087</v>
+        <v>-2.0487</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4991</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6206</v>
+        <v>1.8674</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8719</v>
+        <v>1.1235</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7487</v>
+        <v>0.7438</v>
       </c>
       <c r="V3" t="n">
-        <v>0.705</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.705</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6142</v>
+        <v>1.0716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1094</v>
+        <v>1.3028</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5048</v>
+        <v>-0.2312</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.04</v>
+        <v>1.8604</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0391</v>
+        <v>0.9681</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0792</v>
+        <v>0.8924</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4184</v>
+        <v>2.0325</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8957</v>
+        <v>1.3994</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4774</v>
+        <v>0.633</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4584</v>
+        <v>-0.172</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8566</v>
+        <v>-0.4314</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6018</v>
+        <v>0.2593</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6816</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0447</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7262</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9045</v>
+        <v>0.3006</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4169</v>
+        <v>0.4085</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4876</v>
+        <v>-0.1078</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9318</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3188</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2507</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8536</v>
+        <v>0.5787</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3141</v>
+        <v>-1.2181</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4604</v>
+        <v>1.7968</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8621</v>
+        <v>-3.8133</v>
       </c>
       <c r="H5" t="n">
-        <v>0.97</v>
+        <v>-1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8921</v>
+        <v>-2.4833</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0396</v>
+        <v>-2.6956</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4058</v>
+        <v>-0.4384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6338</v>
+        <v>-2.2572</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1775</v>
+        <v>-1.1177</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4358</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2583</v>
+        <v>-0.226</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-0.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1359</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0828</v>
+        <v>2.0961</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4104</v>
+        <v>1.6855</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3276</v>
+        <v>0.4105</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0913</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7171</v>
+        <v>0.4018</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6947</v>
+        <v>-0.6586</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4118</v>
+        <v>1.0604</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2896</v>
+        <v>0.2792</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9213</v>
+        <v>1.9086</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6317</v>
+        <v>-1.6294</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8907</v>
+        <v>1.8694</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6051</v>
+        <v>2.5846</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6012</v>
+        <v>-1.5902</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6838</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4078</v>
+        <v>3.4145</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.3714</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0186</v>
+        <v>0.0458</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6964</v>
+        <v>0.3256</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.4298</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1885</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4269</v>
+        <v>-0.3584</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1897</v>
+        <v>0.1904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1378</v>
+        <v>0.1387</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0891</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1005</v>
+        <v>0.1014</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1005</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.236</v>
+        <v>-0.0558</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2776</v>
+        <v>-0.1604</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0416</v>
+        <v>0.1046</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.471</v>
+        <v>-1.2785</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9798</v>
+        <v>-0.9714</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4911</v>
+        <v>-0.3071</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4561</v>
+        <v>-1.5035</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0173</v>
+        <v>-0.4738</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4733</v>
+        <v>-1.0297</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7716</v>
+        <v>0.1721</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0173</v>
+        <v>0.389</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7889</v>
+        <v>-0.2169</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3156</v>
+        <v>-1.6756</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8628</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3156</v>
+        <v>-0.8129</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0487</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.4145</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07630000000000001</v>
+        <v>1.1959</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2082</v>
+        <v>0.9052</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2846</v>
+        <v>0.2908</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0913</v>
+        <v>-2.3367</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8393</v>
+        <v>-1.5634</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0756</v>
+        <v>-0.9815</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9149</v>
+        <v>-0.5819</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8411</v>
+        <v>-0.4565</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.411</v>
+        <v>0.0172</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4301</v>
+        <v>-0.4738</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7198</v>
+        <v>-0.7724</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7198</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1213</v>
+        <v>0.3159</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6913</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4301</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4544</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5709</v>
+        <v>-0.0174</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0225</v>
+        <v>-0.2091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5483</v>
+        <v>0.1917</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7963</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7963</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.21</v>
+        <v>-2.5732</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4371</v>
+        <v>-0.4492</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7729</v>
+        <v>-2.124</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5006</v>
+        <v>-1.839</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4733</v>
+        <v>-1.4102</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0272</v>
+        <v>-0.4289</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1879</v>
+        <v>-0.7207</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3983</v>
+        <v>-0.7207</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2104</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6885</v>
+        <v>-1.1184</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8716</v>
+        <v>-0.6895</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8169</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3631</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0447</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4078</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7306</v>
+        <v>0.8302</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5803</v>
+        <v>0.4991</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1504</v>
+        <v>0.3311</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.3419</v>
+        <v>-1.792</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3419</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0978</v>
+        <v>-5.8112</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6524</v>
+        <v>-5.5944</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4454</v>
+        <v>-0.2168</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.2253</v>
+        <v>-6.2302</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.1541</v>
+        <v>-4.1578</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0711</v>
+        <v>-2.0723</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.905</v>
+        <v>-5.9147</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.5756</v>
+        <v>-3.583</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.3294</v>
+        <v>-2.3317</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3203</v>
+        <v>-0.3155</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5786</v>
+        <v>-0.5749</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2583</v>
+        <v>0.2593</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0828</v>
+        <v>0.3703</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2526</v>
+        <v>0.3202</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1698</v>
+        <v>0.0501</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.7369</v>
+        <v>-7.8543</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.706300000000001</v>
+        <v>-8.3139</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0306</v>
+        <v>0.4596</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6572</v>
+        <v>-5.659</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1894</v>
+        <v>-2.191</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.4678</v>
+        <v>-3.4681</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.3988</v>
+        <v>-4.4123</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3178</v>
+        <v>-1.3282</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.081</v>
+        <v>-3.0841</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2584</v>
+        <v>-1.2467</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8716</v>
+        <v>-0.8628</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3868</v>
+        <v>-0.384</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.3612</v>
+        <v>-6.3737</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2175</v>
+        <v>0.6745</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4169</v>
+        <v>0.8379</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6344</v>
+        <v>-0.1634</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6369</v>
+        <v>1.6342</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.977</v>
+        <v>-11.6302</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.0084</v>
+        <v>-13.8343</v>
       </c>
       <c r="F13" t="n">
-        <v>2.031600000000001</v>
+        <v>2.203999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.3218</v>
+        <v>-14.3453</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.4935</v>
+        <v>-3.515</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.8282</v>
+        <v>-10.8304</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.2925</v>
+        <v>-6.3961</v>
       </c>
       <c r="K13" t="n">
-        <v>2.818099999999999</v>
+        <v>2.739000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.1106</v>
+        <v>-9.135199999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.029299999999999</v>
+        <v>-7.9493</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.3118</v>
+        <v>-6.254099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7176</v>
+        <v>-1.6955</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0389</v>
+        <v>-17.0724</v>
       </c>
       <c r="R13" t="n">
-        <v>19.3108</v>
+        <v>19.3488</v>
       </c>
       <c r="S13" t="n">
-        <v>8.962400000000001</v>
+        <v>9.3124</v>
       </c>
       <c r="T13" t="n">
-        <v>6.5029</v>
+        <v>6.823900000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4593</v>
+        <v>2.4885</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.8896</v>
+        <v>-8.8736</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8201</v>
+        <v>2.81</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.7099</v>
+        <v>-11.6836</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2168</v>
+        <v>5.0899</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6609</v>
+        <v>3.3245</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5559</v>
+        <v>1.7654</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5803</v>
+        <v>2.5775</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6748</v>
+        <v>2.6713</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0945</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2187</v>
+        <v>2.2029</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0881</v>
+        <v>3.0747</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8718</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3616</v>
+        <v>0.3746</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4133</v>
+        <v>-0.4034</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7749</v>
+        <v>0.778</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>0.248</v>
+        <v>-0.8651</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3256</v>
+        <v>0.0205</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0776</v>
+        <v>-0.8855</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5244</v>
+        <v>4.5157</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5244</v>
+        <v>4.5157</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0285</v>
+        <v>5.0484</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9389</v>
+        <v>2.2854</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0896</v>
+        <v>2.763</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5513</v>
+        <v>1.5568</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8197</v>
+        <v>0.8237</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3223</v>
+        <v>-0.3242</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4666</v>
+        <v>0.4654</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8736</v>
+        <v>1.881</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3531</v>
+        <v>0.3583</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5206</v>
+        <v>1.5228</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2956</v>
+        <v>-0.2808</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4669</v>
+        <v>-0.1141</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1712</v>
+        <v>-0.1667</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7281</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7372</v>
+        <v>2.8662</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.065</v>
+        <v>1.2979</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8021</v>
+        <v>1.5682</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1688</v>
+        <v>3.3865</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1886</v>
+        <v>1.9664</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3574</v>
+        <v>1.42</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2766</v>
+        <v>1.663</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6981000000000001</v>
+        <v>1.5513</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5785</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8922</v>
+        <v>1.7234</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8867</v>
+        <v>0.4151</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7789</v>
+        <v>1.3083</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3631</v>
+        <v>2.5039</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4078</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0447</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.546</v>
+        <v>-1.39</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.025</v>
+        <v>-0.3651</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.521</v>
+        <v>-1.025</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4775</v>
+        <v>-1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3862</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6966</v>
+        <v>1.9637</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7144</v>
+        <v>-1.3321</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9821</v>
+        <v>3.2959</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3783</v>
+        <v>2.163</v>
       </c>
       <c r="H17" t="n">
-        <v>1.961</v>
+        <v>-0.1919</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4174</v>
+        <v>2.3549</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6672</v>
+        <v>1.258</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5553</v>
+        <v>0.6853</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1118</v>
+        <v>0.5728</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7112</v>
+        <v>0.9049</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4056</v>
+        <v>-0.8772</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3055</v>
+        <v>1.7821</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4991</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4991</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5439</v>
+        <v>-0.3099</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9527</v>
+        <v>-0.2652</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5912</v>
+        <v>-0.0447</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6369</v>
+        <v>1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6369</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7948</v>
+        <v>0.6828</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3054</v>
+        <v>-0.4425</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1001</v>
+        <v>1.1254</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2672</v>
+        <v>1.2735</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1421</v>
+        <v>-1.1353</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4093</v>
+        <v>2.4088</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2663</v>
+        <v>1.258</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3681</v>
+        <v>-0.3727</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0009</v>
+        <v>0.0154</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.774</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7749</v>
+        <v>0.778</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4043</v>
+        <v>-1.5224</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.391</v>
+        <v>-0.5138</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0133</v>
+        <v>-1.0086</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2212</v>
+        <v>0.0184</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5432</v>
+        <v>0.4322</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7645</v>
+        <v>-0.4138</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1487</v>
+        <v>0.2994</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2059</v>
+        <v>0.3187</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0573</v>
+        <v>-0.0193</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6142</v>
+        <v>0.5716</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4464</v>
+        <v>0.5343</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8322000000000001</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5344</v>
+        <v>-0.2722</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2405</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7749</v>
+        <v>-0.0565</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9534</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5437</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5903</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3892</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0444</v>
+        <v>-0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3448</v>
+        <v>-0.3692</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6369</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3419</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0455</v>
+        <v>-0.0485</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4342</v>
+        <v>-1.8088</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4797</v>
+        <v>1.7602</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2978</v>
+        <v>1.1496</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3178</v>
+        <v>1.2061</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02</v>
+        <v>-0.0565</v>
       </c>
       <c r="J20" t="n">
-        <v>0.573</v>
+        <v>0.6026</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5357</v>
+        <v>1.4372</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0373</v>
+        <v>-0.8345</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2752</v>
+        <v>0.547</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2179</v>
+        <v>-0.231</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0573</v>
+        <v>0.778</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2272</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2272</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5705</v>
+        <v>0.1269</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1388</v>
+        <v>-0.1955</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4317</v>
+        <v>0.3223</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1719</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0843</v>
+        <v>-0.0849</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0877</v>
+        <v>0.011</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2356</v>
+        <v>-0.2322</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2157</v>
+        <v>-0.2129</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.02</v>
+        <v>-0.0193</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0546</v>
+        <v>0.0545</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2902</v>
+        <v>-0.2866</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2329</v>
+        <v>-0.2301</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0573</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5497</v>
+        <v>-0.4564</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4109</v>
+        <v>-0.317</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2453</v>
+        <v>-0.177</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1939</v>
+        <v>-2.7423</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9486</v>
+        <v>2.5652</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8201</v>
+        <v>2.8243</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9633</v>
+        <v>-0.9597</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7834</v>
+        <v>3.7839</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2546</v>
+        <v>1.2455</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5349</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7895</v>
+        <v>1.7874</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5655</v>
+        <v>1.5787</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4284</v>
+        <v>-0.4179</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9939</v>
+        <v>1.9966</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3843</v>
+        <v>-1.3168</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8139</v>
+        <v>-0.3441</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5704</v>
+        <v>-0.9727</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2554</v>
+        <v>-1.8119</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5882</v>
+        <v>-3.1335</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3329</v>
+        <v>1.3216</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6552</v>
+        <v>-0.6528</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.976</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3209</v>
+        <v>0.3185</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5735</v>
+        <v>-0.5826</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5928</v>
+        <v>-0.5968</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0193</v>
+        <v>0.0142</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3833</v>
+        <v>-0.3745</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3016</v>
+        <v>0.3043</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3053</v>
+        <v>-0.8615</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9023</v>
+        <v>-0.4324</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.403</v>
+        <v>-0.4292</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.977</v>
+        <v>13.5581</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0316</v>
+        <v>-2.204100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>14.0084</v>
+        <v>15.7621</v>
       </c>
       <c r="G24" t="n">
-        <v>14.3217</v>
+        <v>14.3456</v>
       </c>
       <c r="H24" t="n">
-        <v>3.493499999999999</v>
+        <v>3.515099999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>10.8283</v>
+        <v>10.8304</v>
       </c>
       <c r="J24" t="n">
-        <v>8.029400000000001</v>
+        <v>7.9493</v>
       </c>
       <c r="K24" t="n">
-        <v>6.311699999999998</v>
+        <v>6.254099999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>1.7175</v>
+        <v>1.6954</v>
       </c>
       <c r="M24" t="n">
-        <v>6.2923</v>
+        <v>6.395900000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.8183</v>
+        <v>-2.739</v>
       </c>
       <c r="O24" t="n">
-        <v>9.110600000000002</v>
+        <v>9.1351</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2717</v>
+        <v>-2.2765</v>
       </c>
       <c r="Q24" t="n">
-        <v>-19.3109</v>
+        <v>-19.3487</v>
       </c>
       <c r="R24" t="n">
-        <v>17.0392</v>
+        <v>17.0722</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.962399999999999</v>
+        <v>-7.3846</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.4594</v>
+        <v>-2.4885</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.5031</v>
+        <v>-4.8963</v>
       </c>
       <c r="V24" t="n">
-        <v>8.8894</v>
+        <v>8.8736</v>
       </c>
       <c r="W24" t="n">
-        <v>11.7096</v>
+        <v>11.6837</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8201</v>
+        <v>-2.8099</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104723_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104723_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-11.6836</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104723_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-2.8099</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
